--- a/artfynd/A 10455-2022 artfynd.xlsx
+++ b/artfynd/A 10455-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121124795</v>
       </c>
       <c r="B2" t="n">
-        <v>103000</v>
+        <v>103010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10455-2022 artfynd.xlsx
+++ b/artfynd/A 10455-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121124795</v>
       </c>
       <c r="B2" t="n">
-        <v>103010</v>
+        <v>103023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10455-2022 artfynd.xlsx
+++ b/artfynd/A 10455-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121124795</v>
       </c>
       <c r="B2" t="n">
-        <v>103023</v>
+        <v>103024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10455-2022 artfynd.xlsx
+++ b/artfynd/A 10455-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121124795</v>
       </c>
       <c r="B2" t="n">
-        <v>103024</v>
+        <v>103027</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 10455-2022 artfynd.xlsx
+++ b/artfynd/A 10455-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121124795</v>
+        <v>56091393</v>
       </c>
       <c r="B2" t="n">
-        <v>103027</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>vägen ut till Själgrund, Upl</t>
+          <t>Själgrundsvägen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643381</v>
+        <v>643398</v>
       </c>
       <c r="R2" t="n">
-        <v>6723278</v>
+        <v>6723279</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2015-05-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,6 +778,329 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67980248</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103691</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222009</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sandviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Viola rupestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>väg 600 m S om Gårdskärshamn, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>643402</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6723277</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-05-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-05-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96940553</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103691</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222009</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sandviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola rupestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalvören, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>643391</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6723279</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Några plantor har överlevt makadam- täckning</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121124795</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103691</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222009</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sandviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Viola rupestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>vägen ut till Själgrund, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>643381</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6723278</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10455-2022 artfynd.xlsx
+++ b/artfynd/A 10455-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940553</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,8 +1121,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124795</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>